--- a/resources/templates/standard/H1100-01.xlsx
+++ b/resources/templates/standard/H1100-01.xlsx
@@ -11,7 +11,10 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="32" uniqueCount="31">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="33" uniqueCount="32">
+  <si>
+    <t>{{companyLogo}}</t>
+  </si>
   <si>
     <t>제조 타당성 검토서</t>
   </si>
@@ -872,10 +875,12 @@
   </cols>
   <sheetData>
     <row r="1" ht="21" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A1" s="1"/>
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
       <c r="B1" s="1"/>
       <c r="C1" s="2" t="s">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D1" s="2"/>
       <c r="E1" s="2"/>
@@ -884,16 +889,16 @@
       <c r="H1" s="2"/>
       <c r="I1" s="2"/>
       <c r="J1" s="3" t="s">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K1" s="4" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L1" s="4" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="M1" s="5" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="2" ht="21" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
@@ -943,7 +948,7 @@
     </row>
     <row r="5" ht="18" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A5" s="10" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B5" s="10"/>
       <c r="C5" s="11"/>
@@ -951,7 +956,7 @@
       <c r="E5" s="11"/>
       <c r="F5" s="11"/>
       <c r="G5" s="4" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="H5" s="4"/>
       <c r="I5" s="12"/>
@@ -962,7 +967,7 @@
     </row>
     <row r="6" ht="18" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A6" s="13" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="B6" s="13"/>
       <c r="C6" s="14"/>
@@ -970,7 +975,7 @@
       <c r="E6" s="14"/>
       <c r="F6" s="14"/>
       <c r="G6" s="15" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="H6" s="15"/>
       <c r="I6" s="16"/>
@@ -981,7 +986,7 @@
     </row>
     <row r="7" ht="18" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A7" s="13" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B7" s="13"/>
       <c r="C7" s="14"/>
@@ -989,7 +994,7 @@
       <c r="E7" s="14"/>
       <c r="F7" s="14"/>
       <c r="G7" s="15" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="H7" s="15"/>
       <c r="I7" s="16"/>
@@ -1000,19 +1005,19 @@
     </row>
     <row r="8" ht="18" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A8" s="17" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B8" s="17"/>
       <c r="C8" s="17"/>
       <c r="D8" s="17"/>
       <c r="E8" s="18" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F8" s="18"/>
       <c r="G8" s="18"/>
       <c r="H8" s="18"/>
       <c r="I8" s="18" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="J8" s="18"/>
       <c r="K8" s="18"/>
@@ -1111,7 +1116,7 @@
     </row>
     <row r="15" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A15" s="19" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B15" s="20"/>
       <c r="C15" s="20"/>
@@ -1188,7 +1193,7 @@
     </row>
     <row r="20" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A20" s="31" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B20" s="30"/>
       <c r="C20" s="30"/>
@@ -1235,7 +1240,7 @@
     </row>
     <row r="23" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A23" s="19" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B23" s="20"/>
       <c r="C23" s="20"/>
@@ -1253,7 +1258,7 @@
     <row r="24" ht="11.25" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A24" s="19"/>
       <c r="B24" s="20" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C24" s="20"/>
       <c r="D24" s="20"/>
@@ -1284,7 +1289,7 @@
     </row>
     <row r="26" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A26" s="31" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B26" s="30"/>
       <c r="C26" s="30"/>
@@ -1331,7 +1336,7 @@
     </row>
     <row r="29" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A29" s="19" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B29" s="20"/>
       <c r="C29" s="20"/>
@@ -1349,7 +1354,7 @@
     <row r="30" ht="11.25" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A30" s="19"/>
       <c r="B30" s="20" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C30" s="20"/>
       <c r="D30" s="20"/>
@@ -1380,7 +1385,7 @@
     </row>
     <row r="32" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A32" s="19" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B32" s="20"/>
       <c r="C32" s="20"/>
@@ -1427,7 +1432,7 @@
     </row>
     <row r="35" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A35" s="31" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B35" s="30"/>
       <c r="C35" s="30"/>
@@ -1474,7 +1479,7 @@
     </row>
     <row r="38" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A38" s="19" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B38" s="20"/>
       <c r="C38" s="20"/>
@@ -1536,7 +1541,7 @@
     </row>
     <row r="42" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A42" s="31" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B42" s="30"/>
       <c r="C42" s="30"/>
@@ -1583,7 +1588,7 @@
     </row>
     <row r="45" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A45" s="19" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="B45" s="20"/>
       <c r="C45" s="20"/>
@@ -1630,18 +1635,18 @@
     </row>
     <row r="48" ht="18.75" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A48" s="34" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="B48" s="34"/>
       <c r="C48" s="15" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="D48" s="15"/>
       <c r="E48" s="14"/>
       <c r="F48" s="14"/>
       <c r="G48" s="14"/>
       <c r="H48" s="15" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="I48" s="15"/>
       <c r="J48" s="15"/>
@@ -1653,14 +1658,14 @@
       <c r="A49" s="34"/>
       <c r="B49" s="34"/>
       <c r="C49" s="15" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D49" s="15"/>
       <c r="E49" s="14"/>
       <c r="F49" s="14"/>
       <c r="G49" s="14"/>
       <c r="H49" s="15" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="I49" s="15"/>
       <c r="J49" s="15"/>
@@ -1672,7 +1677,7 @@
       <c r="A50" s="34"/>
       <c r="B50" s="34"/>
       <c r="C50" s="35" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="D50" s="35"/>
       <c r="E50" s="36"/>
